--- a/山林所得の計算のしかたexcel.xlsx
+++ b/山林所得の計算のしかたexcel.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\personal\篤美\相続税\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B8B1957-0C5C-48CE-B3AD-39A7D430F6BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4661A83F-65F8-48DC-BA0A-2E860EC4E8BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="山林所得計算" sheetId="1" r:id="rId1"/>
     <sheet name="税率表" sheetId="2" r:id="rId2"/>
+    <sheet name="特例・参考情報" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">山林所得計算!$A$1:$D$45</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">山林所得計算!$A$1:$D$46</definedName>
   </definedNames>
   <calcPr calcId="191029" forceFullCalc="1"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="82">
   <si>
     <t>山林所得・所得税 計算シート</t>
   </si>
@@ -191,6 +192,154 @@
       <t>ケイサン</t>
     </rPh>
     <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>山林所得に関係する主な特例・参考情報</t>
+  </si>
+  <si>
+    <t>このシートの目的</t>
+  </si>
+  <si>
+    <t>山林所得には、一定の条件を満たす場合に利用できる特例があります。このシートでは、特例の存在・概要・確認ポイント・計算方法の参照先を確認できます。</t>
+  </si>
+  <si>
+    <t>特例・制度</t>
+  </si>
+  <si>
+    <t>根拠法令</t>
+  </si>
+  <si>
+    <t>どんな場合の制度か</t>
+  </si>
+  <si>
+    <t>確認したい主なポイント</t>
+  </si>
+  <si>
+    <t>計算方法の概要</t>
+  </si>
+  <si>
+    <t>参照先</t>
+  </si>
+  <si>
+    <t>森林計画特別控除の特例</t>
+  </si>
+  <si>
+    <t>租税特別措置法30条の2</t>
+  </si>
+  <si>
+    <t>森林計画に基づく伐採・譲渡など、一定の要件に該当する場合に関係する特例。</t>
+  </si>
+  <si>
+    <t>対象となる森林計画か／対象となる行為・譲渡か／適用期限やその他の要件</t>
+  </si>
+  <si>
+    <t>対象となる山林所得等を確認し、法令・国税庁の計算方法に従って特別控除額を確認する。</t>
+  </si>
+  <si>
+    <t>国税庁の山林所得案内・租税特別措置法30条の2</t>
+  </si>
+  <si>
+    <t>収用などにより山林を譲渡した場合の特例</t>
+  </si>
+  <si>
+    <t>租税特別措置法33条・33条の4</t>
+  </si>
+  <si>
+    <t>公共事業などのために土地・山林を収用等された場合に関係する特例。</t>
+  </si>
+  <si>
+    <t>収用等に該当するか／5,000万円特別控除の要件／代替資産の取得の有無／特例の選択関係</t>
+  </si>
+  <si>
+    <t>5,000万円特別控除または代替資産の特例など、該当する制度の計算明細を確認する。</t>
+  </si>
+  <si>
+    <t>国税庁の収用特例の案内</t>
+  </si>
+  <si>
+    <t>山林の譲渡代金が貸倒れになった場合の特例</t>
+  </si>
+  <si>
+    <t>所得税法64条1項</t>
+  </si>
+  <si>
+    <t>山林の譲渡代金が回収できず、貸倒れとなった場合に関係する特例。</t>
+  </si>
+  <si>
+    <t>本当に貸倒れに該当するか／山林経営が事業に該当するか／貸倒れの事実・金額を証明できるか</t>
+  </si>
+  <si>
+    <t>貸倒れとなった譲渡代金に対応する山林所得について、適用要件と計算方法を確認する。</t>
+  </si>
+  <si>
+    <t>国税庁の山林所得案内・所得税法64条1項</t>
+  </si>
+  <si>
+    <t>保証債務を履行するため山林を譲渡した場合の特例</t>
+  </si>
+  <si>
+    <t>所得税法64条2項</t>
+  </si>
+  <si>
+    <t>保証債務を履行するために山林を譲渡し、一定の要件を満たす場合に関係する特例。</t>
+  </si>
+  <si>
+    <t>保証債務の履行のための譲渡か／求償権を行使できなくなったか／適用除外に該当しないか</t>
+  </si>
+  <si>
+    <t>保証債務の履行額や求償権に関する状況を確認し、対応する山林所得の計算方法を参照する。</t>
+  </si>
+  <si>
+    <t>国税庁の山林所得案内・所得税法64条2項</t>
+  </si>
+  <si>
+    <t>確認時の注意</t>
+  </si>
+  <si>
+    <t>・このシートは特例の存在を知り、確認するための参考情報です。適用できることを自動判定するものではありません。</t>
+  </si>
+  <si>
+    <t>・特例は適用条件、期限、証明書類、他の制度との選択関係などがあるため、国税庁資料や税務署等で確認してください。</t>
+  </si>
+  <si>
+    <t>・計算方法は、国税庁の申告案内・計算明細書・法令の該当箇所を参照してください。</t>
+  </si>
+  <si>
+    <t>主な参照先</t>
+  </si>
+  <si>
+    <t>国税庁：令和7年分 山林所得の申告のしかた</t>
+  </si>
+  <si>
+    <t>https://www.nta.go.jp/taxes/shiraberu/shinkoku/tebiki/2025/pdf/P/P7.pdf</t>
+  </si>
+  <si>
+    <t>e-Gov法令検索：租税特別措置法</t>
+  </si>
+  <si>
+    <t>https://elaws.e-gov.go.jp/document?lawid=332AC0000000026</t>
+  </si>
+  <si>
+    <t>e-Gov法令検索：所得税法</t>
+  </si>
+  <si>
+    <t>https://elaws.e-gov.go.jp/document?lawid=340AC0000000033</t>
+  </si>
+  <si>
+    <t>・山林所得の税金が軽減される特例についてSheet"特例・参考情報"を参照</t>
+    <rPh sb="26" eb="28">
+      <t>トクレイ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>サンコウ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>サンショウ</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
   </si>
 </sst>
 </file>
@@ -287,7 +436,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -331,6 +480,11 @@
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -399,7 +553,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -436,16 +590,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="176" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -454,6 +598,35 @@
     </xf>
     <xf numFmtId="176" fontId="0" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -506,7 +679,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="$F$3:$O$11" spid="_x0000_s1028"/>
+                  <a14:cameraTool cellRange="$F$3:$O$11" spid="_x0000_s1030"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -2416,7 +2589,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O45"/>
+  <dimension ref="A1:O46"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -2426,12 +2599,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
       <c r="E1" s="13"/>
       <c r="F1" s="13"/>
       <c r="G1" s="13"/>
@@ -2753,18 +2926,18 @@
       <c r="O19" s="13"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A20" s="17" t="s">
+      <c r="A20" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
+      <c r="B20" s="20"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A21" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B21" s="19">
+      <c r="B21" s="15">
         <v>0</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -2776,7 +2949,7 @@
       <c r="A22" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B22" s="18">
+      <c r="B22" s="14">
         <v>0</v>
       </c>
       <c r="C22" s="2" t="s">
@@ -2788,7 +2961,7 @@
       <c r="A23" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B23" s="20">
+      <c r="B23" s="16">
         <f>MIN(B28/2,500000)</f>
         <v>0</v>
       </c>
@@ -2801,7 +2974,7 @@
       <c r="A24" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B24" s="20">
+      <c r="B24" s="16">
         <v>0</v>
       </c>
       <c r="C24" s="2" t="s">
@@ -2822,12 +2995,12 @@
       <c r="D26" s="1"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A27" s="17" t="s">
+      <c r="A27" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="B27" s="15"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
+      <c r="B27" s="20"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="20"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A28" s="2" t="s">
@@ -2935,63 +3108,68 @@
       <c r="D36" s="1"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A37" s="16" t="s">
+      <c r="A37" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="B37" s="15"/>
-      <c r="C37" s="15"/>
-      <c r="D37" s="15"/>
+      <c r="B37" s="20"/>
+      <c r="C37" s="20"/>
+      <c r="D37" s="20"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A38" s="16" t="s">
+      <c r="A38" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="B38" s="15"/>
-      <c r="C38" s="15"/>
-      <c r="D38" s="15"/>
+      <c r="B38" s="20"/>
+      <c r="C38" s="20"/>
+      <c r="D38" s="20"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A39" s="16" t="s">
+      <c r="A39" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="B39" s="15"/>
-      <c r="C39" s="15"/>
-      <c r="D39" s="15"/>
+      <c r="B39" s="20"/>
+      <c r="C39" s="20"/>
+      <c r="D39" s="20"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A40" s="16" t="s">
+      <c r="A40" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="B40" s="15"/>
-      <c r="C40" s="15"/>
-      <c r="D40" s="15"/>
+      <c r="B40" s="20"/>
+      <c r="C40" s="20"/>
+      <c r="D40" s="20"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A41" s="16" t="s">
+      <c r="A41" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A42" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="B41" s="15"/>
-      <c r="C41" s="15"/>
-      <c r="D41" s="15"/>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A43" t="s">
-        <v>34</v>
-      </c>
+      <c r="B42" s="20"/>
+      <c r="C42" s="20"/>
+      <c r="D42" s="20"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A45" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A45" s="11" t="s">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A46" s="11" t="s">
         <v>35</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="A42:D42"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A40:D40"/>
     <mergeCell ref="A39:D39"/>
@@ -3007,10 +3185,10 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="A45" r:id="rId1" xr:uid="{14228587-1E19-4A30-9128-1440925B4031}"/>
+    <hyperlink ref="A46" r:id="rId1" xr:uid="{14228587-1E19-4A30-9128-1440925B4031}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" scale="54" orientation="landscape" r:id="rId2"/>
+  <pageSetup paperSize="9" scale="52" orientation="landscape" r:id="rId2"/>
   <drawing r:id="rId3"/>
   <legacyDrawing r:id="rId4"/>
 </worksheet>
@@ -3143,4 +3321,252 @@
   <phoneticPr fontId="7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E0DE9B9-B3C5-4119-AE7F-DA08DEB98E84}">
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="4" max="4" width="48" customWidth="1"/>
+    <col min="5" max="5" width="42" customWidth="1"/>
+    <col min="6" max="6" width="45" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="21.75" x14ac:dyDescent="0.4">
+      <c r="A1" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A3" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A4" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A6" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A13" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A14" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A15" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A16" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A18" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+    </row>
+    <row r="19" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A19" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="B19" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+    </row>
+    <row r="20" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A20" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="B20" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A21" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="B21" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="B21:F21"/>
+  </mergeCells>
+  <phoneticPr fontId="7"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/山林所得の計算のしかたexcel.xlsx
+++ b/山林所得の計算のしかたexcel.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\personal\篤美\相続税\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pukkun\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4661A83F-65F8-48DC-BA0A-2E860EC4E8BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E773DC0-A4C8-41FF-8EAE-01CCB45B38A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="83">
   <si>
     <t>山林所得・所得税 計算シート</t>
   </si>
@@ -338,6 +338,13 @@
     </rPh>
     <rPh sb="35" eb="37">
       <t>サンショウ</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>(課税される山林所得金額 ×5分の1× 税率)× 5　－控除額</t>
+    <rPh sb="28" eb="31">
+      <t>コウジョガク</t>
     </rPh>
     <phoneticPr fontId="7"/>
   </si>
@@ -553,21 +560,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -579,54 +574,74 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="2" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="176" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="2" applyFill="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyProtection="1"/>
+    <xf numFmtId="176" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -679,7 +694,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="$F$3:$O$11" spid="_x0000_s1030"/>
+                  <a14:cameraTool cellRange="$F$3:$O$11" spid="_x0000_s1032"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -2592,582 +2607,584 @@
   <dimension ref="A1:O46"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="52" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="1" max="1" width="34" style="16" customWidth="1"/>
+    <col min="2" max="2" width="20" style="16" customWidth="1"/>
+    <col min="3" max="3" width="52" style="16" customWidth="1"/>
+    <col min="4" max="4" width="18" style="16" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="16"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="13"/>
-      <c r="O2" s="13"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="15"/>
+      <c r="O2" s="15"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="13"/>
-      <c r="M3" s="13"/>
-      <c r="N3" s="13"/>
-      <c r="O3" s="13"/>
+      <c r="A3" s="18"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
+      <c r="K3" s="15"/>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15"/>
+      <c r="N3" s="15"/>
+      <c r="O3" s="15"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
-      <c r="M4" s="13"/>
-      <c r="N4" s="13"/>
-      <c r="O4" s="13"/>
+      <c r="A4" s="18"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
+      <c r="O4" s="15"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
-      <c r="L5" s="13"/>
-      <c r="M5" s="13"/>
-      <c r="N5" s="13"/>
-      <c r="O5" s="13"/>
+      <c r="A5" s="18"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="15"/>
+      <c r="N5" s="15"/>
+      <c r="O5" s="15"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="13"/>
-      <c r="N6" s="13"/>
-      <c r="O6" s="13"/>
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="15"/>
+      <c r="O6" s="15"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
-      <c r="L7" s="13"/>
-      <c r="M7" s="13"/>
-      <c r="N7" s="13"/>
-      <c r="O7" s="13"/>
+      <c r="A7" s="18"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="15"/>
+      <c r="I7" s="15"/>
+      <c r="J7" s="15"/>
+      <c r="K7" s="15"/>
+      <c r="L7" s="15"/>
+      <c r="M7" s="15"/>
+      <c r="N7" s="15"/>
+      <c r="O7" s="15"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="13"/>
-      <c r="M8" s="13"/>
-      <c r="N8" s="13"/>
-      <c r="O8" s="13"/>
+      <c r="A8" s="18"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="15"/>
+      <c r="M8" s="15"/>
+      <c r="N8" s="15"/>
+      <c r="O8" s="15"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="13"/>
-      <c r="M9" s="13"/>
-      <c r="N9" s="13"/>
-      <c r="O9" s="13"/>
+      <c r="A9" s="18"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="15"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="15"/>
+      <c r="M9" s="15"/>
+      <c r="N9" s="15"/>
+      <c r="O9" s="15"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="13"/>
-      <c r="M10" s="13"/>
-      <c r="N10" s="13"/>
-      <c r="O10" s="13"/>
+      <c r="A10" s="18"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
+      <c r="N10" s="15"/>
+      <c r="O10" s="15"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="13"/>
-      <c r="M11" s="13"/>
-      <c r="N11" s="13"/>
-      <c r="O11" s="13"/>
+      <c r="A11" s="18"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="15"/>
+      <c r="L11" s="15"/>
+      <c r="M11" s="15"/>
+      <c r="N11" s="15"/>
+      <c r="O11" s="15"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="13"/>
-      <c r="M12" s="13"/>
-      <c r="N12" s="13"/>
-      <c r="O12" s="13"/>
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="15"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="15"/>
+      <c r="N12" s="15"/>
+      <c r="O12" s="15"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="13"/>
-      <c r="K13" s="13"/>
-      <c r="L13" s="13"/>
-      <c r="M13" s="13"/>
-      <c r="N13" s="13"/>
-      <c r="O13" s="13"/>
+      <c r="A13" s="18"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="15"/>
+      <c r="O13" s="15"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="13"/>
-      <c r="K14" s="13"/>
-      <c r="L14" s="13"/>
-      <c r="M14" s="13"/>
-      <c r="N14" s="13"/>
-      <c r="O14" s="13"/>
+      <c r="A14" s="18"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="15"/>
+      <c r="O14" s="15"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="13"/>
-      <c r="L15" s="13"/>
-      <c r="M15" s="13"/>
-      <c r="N15" s="13"/>
-      <c r="O15" s="13"/>
+      <c r="A15" s="18"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="15"/>
+      <c r="M15" s="15"/>
+      <c r="N15" s="15"/>
+      <c r="O15" s="15"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="13"/>
-      <c r="K16" s="13"/>
-      <c r="L16" s="13"/>
-      <c r="M16" s="13"/>
-      <c r="N16" s="13"/>
-      <c r="O16" s="13"/>
+      <c r="A16" s="18"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="15"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="15"/>
+      <c r="L16" s="15"/>
+      <c r="M16" s="15"/>
+      <c r="N16" s="15"/>
+      <c r="O16" s="15"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="13"/>
-      <c r="K17" s="13"/>
-      <c r="L17" s="13"/>
-      <c r="M17" s="13"/>
-      <c r="N17" s="13"/>
-      <c r="O17" s="13"/>
+      <c r="A17" s="18"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="15"/>
+      <c r="M17" s="15"/>
+      <c r="N17" s="15"/>
+      <c r="O17" s="15"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13"/>
-      <c r="L18" s="13"/>
-      <c r="M18" s="13"/>
-      <c r="N18" s="13"/>
-      <c r="O18" s="13"/>
+      <c r="A18" s="18"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="15"/>
+      <c r="L18" s="15"/>
+      <c r="M18" s="15"/>
+      <c r="N18" s="15"/>
+      <c r="O18" s="15"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="13"/>
-      <c r="J19" s="13"/>
-      <c r="K19" s="13"/>
-      <c r="L19" s="13"/>
-      <c r="M19" s="13"/>
-      <c r="N19" s="13"/>
-      <c r="O19" s="13"/>
+      <c r="A19" s="18"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="15"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="15"/>
+      <c r="L19" s="15"/>
+      <c r="M19" s="15"/>
+      <c r="N19" s="15"/>
+      <c r="O19" s="15"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A20" s="22" t="s">
+      <c r="A20" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="B20" s="20"/>
-      <c r="C20" s="20"/>
-      <c r="D20" s="20"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="B21" s="15">
+      <c r="B21" s="28">
         <v>0</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="D21" s="1"/>
+      <c r="D21" s="18"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="B22" s="14">
+      <c r="B22" s="29">
         <v>0</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D22" s="1"/>
+      <c r="D22" s="18"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="B23" s="16">
+      <c r="B23" s="30">
         <f>MIN(B28/2,500000)</f>
         <v>0</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="D23" s="1"/>
+      <c r="D23" s="18"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="B24" s="16">
+      <c r="B24" s="30">
         <v>0</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="D24" s="1"/>
+      <c r="D24" s="18"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
+      <c r="A25" s="18"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
+      <c r="A26" s="18"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A27" s="22" t="s">
+      <c r="A27" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="B27" s="20"/>
-      <c r="C27" s="20"/>
-      <c r="D27" s="20"/>
+      <c r="B27" s="14"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="B28" s="3">
+      <c r="B28" s="22">
         <f>MAX(0,B21-B22)</f>
         <v>0</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="D28" s="1"/>
+      <c r="D28" s="18"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="B29" s="3">
+      <c r="B29" s="22">
         <f>MAX(0,B28-MIN(B23,B28)-MIN(B24,MAX(0,B28-MIN(B23,B28))))</f>
         <v>0</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="D29" s="1"/>
+      <c r="D29" s="18"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="B30" s="3">
+      <c r="B30" s="22">
         <f>ROUNDDOWN(B29,-3)</f>
         <v>0</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="D30" s="1"/>
+      <c r="D30" s="18"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="B31" s="4">
+      <c r="B31" s="23">
         <f>IF(B30&lt;1000,0,VLOOKUP(B30,税率表!$A$2:$C$8,2,TRUE))</f>
         <v>0</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="D31" s="1"/>
+      <c r="D31" s="18"/>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="B32" s="3">
+      <c r="B32" s="22">
         <f>IF(B30&lt;1000,0,VLOOKUP(B30,税率表!$A$2:$C$8,3,TRUE))</f>
         <v>0</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="D32" s="1"/>
+      <c r="D32" s="18"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="B33" s="3">
-        <f>MAX(0,ROUNDDOWN(B30*B31-B32,0))</f>
+      <c r="B33" s="22">
+        <f>MAX(0,ROUNDDOWN(ROUNDDOWN(B30/5*B31,0)*5-B32,0))</f>
         <v>0</v>
       </c>
-      <c r="C33" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D33" s="1"/>
+      <c r="C33" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="D33" s="18"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A34" s="10" t="s">
+      <c r="A34" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="B34" s="3">
+      <c r="B34" s="22">
         <f>ROUNDDOWN(B33,-3)</f>
         <v>0</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="D34" s="1"/>
+      <c r="D34" s="18"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A35" s="1"/>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
+      <c r="A35" s="18"/>
+      <c r="B35" s="18"/>
+      <c r="C35" s="18"/>
+      <c r="D35" s="18"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A36" s="5" t="s">
+      <c r="A36" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
+      <c r="B36" s="18"/>
+      <c r="C36" s="18"/>
+      <c r="D36" s="18"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A37" s="19" t="s">
+      <c r="A37" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="B37" s="20"/>
-      <c r="C37" s="20"/>
-      <c r="D37" s="20"/>
+      <c r="B37" s="14"/>
+      <c r="C37" s="14"/>
+      <c r="D37" s="14"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A38" s="19" t="s">
+      <c r="A38" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="B38" s="20"/>
-      <c r="C38" s="20"/>
-      <c r="D38" s="20"/>
+      <c r="B38" s="14"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="14"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A39" s="19" t="s">
+      <c r="A39" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="B39" s="20"/>
-      <c r="C39" s="20"/>
-      <c r="D39" s="20"/>
+      <c r="B39" s="14"/>
+      <c r="C39" s="14"/>
+      <c r="D39" s="14"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A40" s="19" t="s">
+      <c r="A40" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="B40" s="20"/>
-      <c r="C40" s="20"/>
-      <c r="D40" s="20"/>
+      <c r="B40" s="14"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="14"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A41" t="s">
+      <c r="A41" s="16" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A42" s="19" t="s">
+      <c r="A42" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="B42" s="20"/>
-      <c r="C42" s="20"/>
-      <c r="D42" s="20"/>
+      <c r="B42" s="14"/>
+      <c r="C42" s="14"/>
+      <c r="D42" s="14"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A44" t="s">
+      <c r="A44" s="16" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A45" t="s">
+      <c r="A45" s="16" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A46" s="11" t="s">
+      <c r="A46" s="27" t="s">
         <v>35</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="/Tr4sASyJvCqOKSzvRjQFpiOw8LJrzey1c5WE+5BMdzLDh1zJUSWft+Mhzk4x7N7VXhM8GkbLxjOYa0BYhYkEA==" saltValue="4Q4tgqj7K40fWoacJRK1pA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="8">
     <mergeCell ref="A42:D42"/>
     <mergeCell ref="A1:D1"/>
@@ -3206,114 +3223,114 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="2" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A2" s="2">
+      <c r="A2" s="1">
         <v>1000</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="3">
         <v>0.05</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2" s="4">
         <v>0</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A3" s="2">
+      <c r="A3" s="1">
         <v>9750000</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="3">
         <v>0.1</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="4">
         <v>487500</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A4" s="2">
+      <c r="A4" s="1">
         <v>16500000</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="3">
         <v>0.2</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="4">
         <v>2137500</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A5" s="2">
+      <c r="A5" s="1">
         <v>34750000</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="3">
         <v>0.23</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="4">
         <v>3180000</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A6" s="2">
+      <c r="A6" s="1">
         <v>45000000</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="3">
         <v>0.33</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="4">
         <v>7680000</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A7" s="2">
+      <c r="A7" s="1">
         <v>90000000</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="3">
         <v>0.4</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="4">
         <v>13980000</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A8" s="2">
+      <c r="A8" s="1">
         <v>200000000</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="3">
         <v>0.45</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="4">
         <v>23980000</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="1" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3337,234 +3354,234 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21.75" x14ac:dyDescent="0.4">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="F6" s="17" t="s">
+      <c r="F6" s="5" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="F7" s="6" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="E8" s="18" t="s">
+      <c r="E8" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="F8" s="18" t="s">
+      <c r="F8" s="6" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="F9" s="18" t="s">
+      <c r="F9" s="6" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E10" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="F10" s="18" t="s">
+      <c r="F10" s="6" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A13" s="24" t="s">
+      <c r="A13" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="B13" s="20"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A14" s="23" t="s">
+      <c r="A14" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A15" s="23" t="s">
+      <c r="A15" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="B15" s="20"/>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A16" s="23" t="s">
+      <c r="A16" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="B16" s="20"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A18" s="24" t="s">
+      <c r="A18" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="B18" s="20"/>
-      <c r="C18" s="20"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="20"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
     </row>
     <row r="19" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A19" s="18" t="s">
+      <c r="A19" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B19" s="25" t="s">
+      <c r="B19" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="C19" s="20"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
     </row>
     <row r="20" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A20" s="18" t="s">
+      <c r="A20" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="B20" s="25" t="s">
+      <c r="B20" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="C20" s="20"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="20"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A21" s="18" t="s">
+      <c r="A21" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="B21" s="25" t="s">
+      <c r="B21" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="C21" s="20"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="20"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="B21:F21"/>
     <mergeCell ref="A15:F15"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="B21:F21"/>
   </mergeCells>
   <phoneticPr fontId="7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
